--- a/PADRAO 8 HS.xlsx
+++ b/PADRAO 8 HS.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr date1904="1"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="13500" yWindow="0" windowWidth="15300" windowHeight="15600" tabRatio="855" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JAN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FEV" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MAR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ABR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MAIO" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JUN" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JUL" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AGO" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SET" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OUT" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOV" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEZ" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="JAN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FEV" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MAR" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ABR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="MAIO" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="JUN" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="JUL" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="AGO" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="SET" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="OUT" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="NOV" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="DEZ" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -5529,594 +5529,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>314326</colOff>
-      <row>0</row>
-      <rowOff>142875</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>447675</colOff>
-      <row>3</row>
-      <rowOff>104775</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Imagem 2"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="923926" y="142875"/>
-          <a:ext cx="742949" cy="600075"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>381001</colOff>
-      <row>0</row>
-      <rowOff>85725</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>28575</colOff>
-      <row>3</row>
-      <rowOff>95250</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Imagem 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="990601" y="85725"/>
-          <a:ext cx="866774" cy="647700"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>381001</colOff>
-      <row>0</row>
-      <rowOff>85725</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>28575</colOff>
-      <row>3</row>
-      <rowOff>95250</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Imagem 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="990601" y="85725"/>
-          <a:ext cx="866774" cy="647700"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>381001</colOff>
-      <row>0</row>
-      <rowOff>85725</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>28575</colOff>
-      <row>3</row>
-      <rowOff>95250</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Imagem 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="990601" y="85725"/>
-          <a:ext cx="866774" cy="647700"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>314326</colOff>
-      <row>0</row>
-      <rowOff>142875</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>47625</colOff>
-      <row>3</row>
-      <rowOff>152400</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Imagem 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="923926" y="142875"/>
-          <a:ext cx="733424" cy="647700"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>314326</colOff>
-      <row>0</row>
-      <rowOff>142875</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>47625</colOff>
-      <row>3</row>
-      <rowOff>152400</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Imagem 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="923926" y="142875"/>
-          <a:ext cx="733424" cy="647700"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>28576</colOff>
-      <row>0</row>
-      <rowOff>133350</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>285750</colOff>
-      <row>3</row>
-      <rowOff>142875</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Imagem 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1247776" y="133350"/>
-          <a:ext cx="704849" cy="647700"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>381001</colOff>
-      <row>0</row>
-      <rowOff>85725</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>28575</colOff>
-      <row>3</row>
-      <rowOff>95250</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Imagem 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="990601" y="85725"/>
-          <a:ext cx="866774" cy="647700"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>381001</colOff>
-      <row>0</row>
-      <rowOff>85725</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>28575</colOff>
-      <row>3</row>
-      <rowOff>95250</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Imagem 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="990601" y="85725"/>
-          <a:ext cx="866774" cy="647700"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>381001</colOff>
-      <row>0</row>
-      <rowOff>85725</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>28575</colOff>
-      <row>3</row>
-      <rowOff>95250</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Imagem 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="990601" y="85725"/>
-          <a:ext cx="866774" cy="647700"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>381001</colOff>
-      <row>0</row>
-      <rowOff>85725</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>28575</colOff>
-      <row>3</row>
-      <rowOff>95250</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Imagem 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="990601" y="85725"/>
-          <a:ext cx="866774" cy="647700"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>381001</colOff>
-      <row>0</row>
-      <rowOff>85725</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>28575</colOff>
-      <row>3</row>
-      <rowOff>95250</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Imagem 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="990601" y="85725"/>
-          <a:ext cx="866774" cy="647700"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -6772,12 +6184,12 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>ENTRADA EXTRA</t>
+          <t>saída EXTRA</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>SAÍDA EXTRA</t>
+          <t>entrada EXTRA</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -9656,7 +9068,6 @@
   </conditionalFormatting>
   <pageMargins left="0.1181102362204725" right="0.1181102362204725" top="0.5905511811023623" bottom="0.3937007874015748" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="portrait" paperSize="9" scale="80"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10019,12 +9430,12 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>ENTRADA EXTRA</t>
+          <t>saída EXTRA</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>SAÍDA EXTRA</t>
+          <t>entrada EXTRA</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -12814,7 +12225,6 @@
   </conditionalFormatting>
   <pageMargins left="0.1181102362204725" right="0.1181102362204725" top="0.5905511811023623" bottom="0.5905511811023623" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="portrait" paperSize="9" scale="80"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -13177,12 +12587,12 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>ENTRADA EXTRA</t>
+          <t>saída EXTRA</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>SAÍDA EXTRA</t>
+          <t>entrada EXTRA</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -15926,7 +15336,6 @@
   </conditionalFormatting>
   <pageMargins left="0.1181102362204725" right="0.1181102362204725" top="0.5905511811023623" bottom="0.7874015748031497" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="portrait" paperSize="9" scale="80"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -16292,12 +15701,12 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>ENTRADA EXTRA</t>
+          <t>saída EXTRA</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>SAÍDA EXTRA</t>
+          <t>entrada EXTRA</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -19106,7 +18515,6 @@
   </conditionalFormatting>
   <pageMargins left="0.1181102362204725" right="0.1181102362204725" top="0.3937007874015748" bottom="0.5905511811023623" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="portrait" paperSize="9" scale="80" horizontalDpi="0" verticalDpi="0"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -19495,12 +18903,12 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>ENTRADA EXTRA</t>
+          <t>saída EXTRA</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>SAÍDA EXTRA</t>
+          <t>entrada EXTRA</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -22488,7 +21896,6 @@
   </conditionalFormatting>
   <pageMargins left="0.1181102362204725" right="0.1181102362204725" top="0.7874015748031497" bottom="0.7874015748031497" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="portrait" paperSize="9" scale="80"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -22858,12 +22265,12 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>ENTRADA EXTRA</t>
+          <t>saída EXTRA</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>SAÍDA EXTRA</t>
+          <t>entrada EXTRA</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -25650,7 +25057,6 @@
   </conditionalFormatting>
   <pageMargins left="0.1181102362204725" right="0.1181102362204725" top="0.5905511811023623" bottom="0.5905511811023623" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="portrait" paperSize="9" scale="80"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -26022,12 +25428,12 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>ENTRADA EXTRA</t>
+          <t>saída EXTRA</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>SAÍDA EXTRA</t>
+          <t>entrada EXTRA</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -26048,7 +25454,7 @@
       <c r="O13" s="47" t="n"/>
       <c r="P13" s="92" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -28765,7 +28171,6 @@
   </conditionalFormatting>
   <pageMargins left="0" right="0" top="0.7874015748031497" bottom="0.5905511811023623" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="portrait" paperSize="9" scale="80"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -29131,12 +28536,12 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>ENTRADA EXTRA</t>
+          <t>saída EXTRA</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>SAÍDA EXTRA</t>
+          <t>entrada EXTRA</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -31931,7 +31336,6 @@
   </conditionalFormatting>
   <pageMargins left="0" right="0" top="0.5905511811023623" bottom="0.5905511811023623" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="portrait" paperSize="9" scale="80"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -32297,12 +31701,12 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>ENTRADA EXTRA</t>
+          <t>saída EXTRA</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>SAÍDA EXTRA</t>
+          <t>entrada EXTRA</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -35050,7 +34454,6 @@
   </conditionalFormatting>
   <pageMargins left="0" right="0" top="0.5905511811023623" bottom="0.7874015748031497" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="portrait" paperSize="9" scale="80"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -35416,12 +34819,12 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>ENTRADA EXTRA</t>
+          <t>saída EXTRA</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>SAÍDA EXTRA</t>
+          <t>entrada EXTRA</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -37993,7 +37396,6 @@
   </conditionalFormatting>
   <pageMargins left="0.1181102362204725" right="0.1181102362204725" top="0.5905511811023623" bottom="0.5905511811023623" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="portrait" paperSize="9" scale="80"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -38359,12 +37761,12 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>ENTRADA EXTRA</t>
+          <t>saída EXTRA</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>SAÍDA EXTRA</t>
+          <t>entrada EXTRA</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -41140,7 +40542,6 @@
   </conditionalFormatting>
   <pageMargins left="0.1181102362204725" right="0.1181102362204725" top="0.5905511811023623" bottom="0.5905511811023623" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="portrait" paperSize="9" scale="80" horizontalDpi="0" verticalDpi="0"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -41502,12 +40903,12 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>ENTRADA EXTRA</t>
+          <t>saída EXTRA</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>SAÍDA EXTRA</t>
+          <t>entrada EXTRA</t>
         </is>
       </c>
       <c r="L13" s="8" t="inlineStr">
@@ -44252,6 +43653,5 @@
   </conditionalFormatting>
   <pageMargins left="0.1181102362204725" right="0.1181102362204725" top="0.5905511811023623" bottom="0.7874015748031497" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="portrait" paperSize="9" scale="80"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>